--- a/Criando um Dashboard de Vendas do Xbox com Excel.xlsx
+++ b/Criando um Dashboard de Vendas do Xbox com Excel.xlsx
@@ -1,34 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29721"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\www\planilhas\dashboard\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B2C12624-F5B9-422D-AABA-2C49D8C07A46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="2" xr2:uid="{28DD5B76-0634-4F87-BE60-8BFA7EF2E23B}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="8220" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="A̳ssets" sheetId="1" r:id="rId1"/>
     <sheet name="B̳ases" sheetId="2" r:id="rId2"/>
-    <sheet name="C̳álculos" sheetId="3" r:id="rId3"/>
-    <sheet name="D̳ashboard" sheetId="4" r:id="rId4"/>
+    <sheet name="Planilha1" sheetId="5" r:id="rId3"/>
+    <sheet name="C̳álculos" sheetId="3" r:id="rId4"/>
+    <sheet name="D̳ashboard" sheetId="4" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="SegmentaçãodeDados_Subscription_Type">#N/A</definedName>
   </definedNames>
-  <calcPr calcId="191028"/>
+  <calcPr calcId="162913"/>
   <pivotCaches>
-    <pivotCache cacheId="402" r:id="rId5"/>
+    <pivotCache cacheId="2" r:id="rId6"/>
   </pivotCaches>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{BBE1A952-AA13-448e-AADC-164F8A28A991}">
       <x14:slicerCaches>
-        <x14:slicerCache r:id="rId6"/>
+        <x14:slicerCache r:id="rId7"/>
       </x14:slicerCaches>
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{79F54976-1DA5-4618-B147-4CDE4B953A38}">
@@ -37,23 +38,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2001" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2206" uniqueCount="319">
   <si>
     <t>Paleta de Cores</t>
   </si>
@@ -1001,15 +991,25 @@
     <t>Total Geral</t>
   </si>
   <si>
-    <t>VENDAS DE SUBSCRIÇÕES DE X-BOX GAME PASS</t>
+    <t>XBOX GAME PASS SUBSCRIPTIONS SALES</t>
+  </si>
+  <si>
+    <t>Soma de EA Play Season Pass</t>
+  </si>
+  <si>
+    <t>Soma de Minecraft Season Pass Price</t>
+  </si>
+  <si>
+    <t>Contagem de Subscription Type</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <numFmts count="2">
+    <numFmt numFmtId="44" formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_-[$R$-416]\ * #,##0.00_-;\-[$R$-416]\ * #,##0.00_-;_-[$R$-416]\ * &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="6">
     <font>
@@ -1128,9 +1128,9 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -1148,20 +1148,60 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Moeda" xfId="2" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Título 1" xfId="1" builtinId="16"/>
   </cellStyles>
-  <dxfs count="14">
+  <dxfs count="17">
+    <dxf>
+      <numFmt numFmtId="19" formatCode="dd/mm/yyyy"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="9"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF2AE6B1"/>
+        </patternFill>
+      </fill>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1205,24 +1245,278 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16">
+    <tableStyle name="XBOX" pivot="0" table="0" count="10">
+      <tableStyleElement type="wholeTable" dxfId="2"/>
+      <tableStyleElement type="headerRow" dxfId="1"/>
+    </tableStyle>
+  </tableStyles>
   <colors>
     <mruColors>
+      <color rgb="FF9BC848"/>
+      <color rgb="FF5BF6A8"/>
+      <color rgb="FF2AE6B1"/>
+      <color rgb="FFE5F1CF"/>
+      <color rgb="FFB5E6A2"/>
       <color rgb="FF22C55E"/>
-      <color rgb="FF2AE6B1"/>
       <color rgb="FFE8E6E9"/>
-      <color rgb="FF5BF6A8"/>
       <color rgb="FF000000"/>
       <color rgb="FFE0E0E0"/>
       <color rgb="FFEDEDED"/>
-      <color rgb="FFF7F8FC"/>
-      <color rgb="FF9BC848"/>
-      <color rgb="FFE70011"/>
     </mruColors>
   </colors>
   <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{46F421CA-312F-682f-3DD2-61675219B42D}">
+      <x14:dxfs count="8">
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <gradientFill degree="90">
+              <stop position="0">
+                <color rgb="FF9BC848"/>
+              </stop>
+              <stop position="1">
+                <color rgb="FFE5F1CF"/>
+              </stop>
+            </gradientFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FF999999"/>
+            </left>
+            <right style="thin">
+              <color rgb="FF999999"/>
+            </right>
+            <top style="thin">
+              <color rgb="FF999999"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FF999999"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <gradientFill degree="90">
+              <stop position="0">
+                <color rgb="FF9BC848"/>
+              </stop>
+              <stop position="1">
+                <color rgb="FFE5F1CF"/>
+              </stop>
+            </gradientFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FF999999"/>
+            </left>
+            <right style="thin">
+              <color rgb="FF999999"/>
+            </right>
+            <top style="thin">
+              <color rgb="FF999999"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FF999999"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <gradientFill degree="90">
+              <stop position="0">
+                <color rgb="FF9BC848"/>
+              </stop>
+              <stop position="1">
+                <color rgb="FFE5F1CF"/>
+              </stop>
+            </gradientFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FF999999"/>
+            </left>
+            <right style="thin">
+              <color rgb="FF999999"/>
+            </right>
+            <top style="thin">
+              <color rgb="FF999999"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FF999999"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <gradientFill degree="90">
+              <stop position="0">
+                <color rgb="FF9BC848"/>
+              </stop>
+              <stop position="1">
+                <color rgb="FFE5F1CF"/>
+              </stop>
+            </gradientFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FF999999"/>
+            </left>
+            <right style="thin">
+              <color rgb="FF999999"/>
+            </right>
+            <top style="thin">
+              <color rgb="FF999999"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FF999999"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF828282"/>
+          </font>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor theme="9" tint="0.79998168889431442"/>
+              <bgColor theme="9" tint="0.79998168889431442"/>
+            </patternFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FFCCCCCC"/>
+            </left>
+            <right style="thin">
+              <color rgb="FFCCCCCC"/>
+            </right>
+            <top style="thin">
+              <color rgb="FFCCCCCC"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FFCCCCCC"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor theme="9" tint="0.59999389629810485"/>
+              <bgColor rgb="FF5BF6A8"/>
+            </patternFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FF999999"/>
+            </left>
+            <right style="thin">
+              <color rgb="FF999999"/>
+            </right>
+            <top style="thin">
+              <color rgb="FF999999"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FF999999"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF828282"/>
+          </font>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor rgb="FFFFFFFF"/>
+              <bgColor rgb="FFFFFFFF"/>
+            </patternFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FFE0E0E0"/>
+            </left>
+            <right style="thin">
+              <color rgb="FFE0E0E0"/>
+            </right>
+            <top style="thin">
+              <color rgb="FFE0E0E0"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FFE0E0E0"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+        <dxf>
+          <font>
+            <color rgb="FF000000"/>
+          </font>
+          <fill>
+            <patternFill patternType="solid">
+              <fgColor rgb="FFFFFFFF"/>
+              <bgColor rgb="FFFFFFFF"/>
+            </patternFill>
+          </fill>
+          <border>
+            <left style="thin">
+              <color rgb="FFCCCCCC"/>
+            </left>
+            <right style="thin">
+              <color rgb="FFCCCCCC"/>
+            </right>
+            <top style="thin">
+              <color rgb="FFCCCCCC"/>
+            </top>
+            <bottom style="thin">
+              <color rgb="FFCCCCCC"/>
+            </bottom>
+            <vertical/>
+            <horizontal/>
+          </border>
+        </dxf>
+      </x14:dxfs>
+    </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1">
+        <x14:slicerStyle name="XBOX">
+          <x14:slicerStyleElements>
+            <x14:slicerStyleElement type="unselectedItemWithData" dxfId="7"/>
+            <x14:slicerStyleElement type="unselectedItemWithNoData" dxfId="6"/>
+            <x14:slicerStyleElement type="selectedItemWithData" dxfId="5"/>
+            <x14:slicerStyleElement type="selectedItemWithNoData" dxfId="4"/>
+            <x14:slicerStyleElement type="hoveredUnselectedItemWithData" dxfId="3"/>
+            <x14:slicerStyleElement type="hoveredSelectedItemWithData" dxfId="2"/>
+            <x14:slicerStyleElement type="hoveredUnselectedItemWithNoData" dxfId="1"/>
+            <x14:slicerStyleElement type="hoveredSelectedItemWithNoData" dxfId="0"/>
+          </x14:slicerStyleElements>
+        </x14:slicerStyle>
+      </x14:slicerStyles>
     </ext>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
       <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
@@ -1246,7 +1540,7 @@
   </mc:AlternateContent>
   <c:pivotSource>
     <c:name>[Criando um Dashboard de Vendas do Xbox com Excel.xlsx]C̳álculos!Tabela dinâmica1</c:name>
-    <c:fmtId val="11"/>
+    <c:fmtId val="31"/>
   </c:pivotSource>
   <c:chart>
     <c:autoTitleDeleted val="1"/>
@@ -1255,7 +1549,7 @@
         <c:idx val="0"/>
         <c:spPr>
           <a:solidFill>
-            <a:srgbClr val="B5E6A2"/>
+            <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:ln>
             <a:noFill/>
@@ -1263,22 +1557,121 @@
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="5"/>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="5BF6A8"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="5BF6A8"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+        <c:dLbl>
+          <c:idx val="0"/>
+          <c:layout/>
           <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
+            <a:noFill/>
+            <a:ln>
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
+          <c:txPr>
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:spAutoFit/>
+            </a:bodyPr>
+            <a:lstStyle/>
+            <a:p>
+              <a:pPr>
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:solidFill>
+                    <a:srgbClr val="5BF6A8"/>
+                  </a:solidFill>
+                  <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+                  <a:ea typeface="+mn-ea"/>
+                  <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+                </a:defRPr>
+              </a:pPr>
+              <a:endParaRPr lang="pt-BR"/>
+            </a:p>
+          </c:txPr>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:spPr xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+                <a:prstGeom prst="wedgeRectCallout">
+                  <a:avLst/>
+                </a:prstGeom>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+              </c15:spPr>
+              <c15:layout/>
+            </c:ext>
+          </c:extLst>
+        </c:dLbl>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:srgbClr val="5BF6A8"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
+          <c:layout/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -1293,270 +1686,30 @@
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
+                    <a:srgbClr val="5BF6A8"/>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="pt-BR"/>
             </a:p>
           </c:txPr>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:layout/>
+            </c:ext>
           </c:extLst>
         </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="1"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:srgbClr val="B5E6A2"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="2"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:srgbClr val="B5E6A2"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="3"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:srgbClr val="B5E6A2"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="4"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:srgbClr val="B5E6A2"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="5"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
@@ -1581,7 +1734,7 @@
           </c:tx>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:srgbClr val="5BF6A8"/>
             </a:solidFill>
             <a:ln>
               <a:noFill/>
@@ -1589,6 +1742,61 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:srgbClr val="5BF6A8"/>
+                    </a:solidFill>
+                    <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="0"/>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
               <c:f>C̳álculos!$C$5:$C$7</c:f>
@@ -1607,7 +1815,7 @@
             <c:numRef>
               <c:f>C̳álculos!$D$5:$D$7</c:f>
               <c:numCache>
-                <c:formatCode>_-"R$"\ * #,##0.00_-;\-"R$"\ * #,##0.00_-;_-"R$"\ * "-"??_-;_-@_-</c:formatCode>
+                <c:formatCode>_("R$"* #,##0.00_);_("R$"* \(#,##0.00\);_("R$"* "-"??_);_(@_)</c:formatCode>
                 <c:ptCount val="2"/>
                 <c:pt idx="0">
                   <c:v>806</c:v>
@@ -1620,7 +1828,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D2CC-491F-9F7A-9E04F6005835}"/>
+              <c16:uniqueId val="{00000000-983A-42A2-8F9F-9E9EBB215AA5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1633,11 +1841,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="182"/>
-        <c:axId val="1711244296"/>
-        <c:axId val="1711246344"/>
+        <c:axId val="1083051504"/>
+        <c:axId val="1083052752"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="1711244296"/>
+        <c:axId val="1083051504"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1665,22 +1873,22 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="900" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="pt-BR"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1711246344"/>
+        <c:crossAx val="1083052752"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1688,37 +1896,23 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1711246344"/>
+        <c:axId val="1083052752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="1"/>
         <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-" sourceLinked="1"/>
+        <c:numFmt formatCode="_(&quot;R$&quot;* #,##0.00_);_(&quot;R$&quot;* \(#,##0.00\);_(&quot;R$&quot;* &quot;-&quot;??_);_(@_)" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1711244296"/>
+        <c:crossAx val="1083051504"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
-        <a:ln>
+        <a:ln w="25400">
           <a:noFill/>
         </a:ln>
         <a:effectLst/>
@@ -1729,16 +1923,9 @@
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
+    <a:noFill/>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
+      <a:noFill/>
       <a:round/>
     </a:ln>
     <a:effectLst/>
@@ -1750,18 +1937,20 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="pt-BR"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
     <c:pageSetup/>
   </c:printSettings>
   <c:extLst>
     <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
       <c14:pivotOptions>
-        <c14:dropZonesVisible val="1"/>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
       </c14:pivotOptions>
     </c:ext>
     <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
@@ -1780,15 +1969,15 @@
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
+      <c14:style val="108"/>
     </mc:Choice>
     <mc:Fallback>
-      <c:style val="2"/>
+      <c:style val="8"/>
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[Criando um Dashboard de Vendas do Xbox com Excel.xlsx]C̳álculos!Tabela dinâmica1</c:name>
-    <c:fmtId val="17"/>
+    <c:name>[Criando um Dashboard de Vendas do Xbox com Excel.xlsx]C̳álculos!Tabela dinâmica4</c:name>
+    <c:fmtId val="35"/>
   </c:pivotSource>
   <c:chart>
     <c:autoTitleDeleted val="1"/>
@@ -1797,30 +1986,207 @@
         <c:idx val="0"/>
         <c:spPr>
           <a:solidFill>
-            <a:srgbClr val="B5E6A2"/>
+            <a:schemeClr val="accent6"/>
           </a:solidFill>
-          <a:ln>
-            <a:noFill/>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
         <c:marker>
-          <c:symbol val="circle"/>
-          <c:size val="5"/>
-          <c:spPr>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="1"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent6"/>
+          </a:solidFill>
+          <a:ln w="19050">
             <a:solidFill>
-              <a:schemeClr val="accent1"/>
+              <a:schemeClr val="lt1"/>
             </a:solidFill>
-            <a:ln w="9525">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="2"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent6"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="3"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent6"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="4"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent6"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="5"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent6"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="6"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent6"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="7"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent6"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="8"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent6"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="9"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent6"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="10"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent6"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="11"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent6"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
+        </c:marker>
+      </c:pivotFmt>
+      <c:pivotFmt>
+        <c:idx val="12"/>
+        <c:spPr>
+          <a:solidFill>
+            <a:schemeClr val="accent6"/>
+          </a:solidFill>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:marker>
+          <c:symbol val="none"/>
         </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
+          <c:layout/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -1829,54 +2195,55 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
               <a:spAutoFit/>
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
+                    <a:schemeClr val="bg1"/>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="pt-BR"/>
             </a:p>
           </c:txPr>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:layout/>
+            </c:ext>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
-        <c:idx val="1"/>
+        <c:idx val="13"/>
         <c:spPr>
           <a:solidFill>
-            <a:srgbClr val="B5E6A2"/>
+            <a:schemeClr val="accent6">
+              <a:tint val="65000"/>
+            </a:schemeClr>
           </a:solidFill>
-          <a:ln>
-            <a:noFill/>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
+          <c:layout/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -1885,54 +2252,53 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
               <a:spAutoFit/>
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
+                    <a:schemeClr val="bg1"/>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="pt-BR"/>
             </a:p>
           </c:txPr>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:layout/>
+            </c:ext>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
-        <c:idx val="2"/>
+        <c:idx val="14"/>
         <c:spPr>
           <a:solidFill>
-            <a:srgbClr val="B5E6A2"/>
+            <a:schemeClr val="accent6"/>
           </a:solidFill>
-          <a:ln>
-            <a:noFill/>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
+          <c:layout/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -1941,54 +2307,55 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
               <a:spAutoFit/>
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
+                    <a:schemeClr val="bg1"/>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="pt-BR"/>
             </a:p>
           </c:txPr>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:layout/>
+            </c:ext>
           </c:extLst>
         </c:dLbl>
       </c:pivotFmt>
       <c:pivotFmt>
-        <c:idx val="3"/>
+        <c:idx val="15"/>
         <c:spPr>
           <a:solidFill>
-            <a:srgbClr val="B5E6A2"/>
+            <a:schemeClr val="accent6">
+              <a:shade val="65000"/>
+            </a:schemeClr>
           </a:solidFill>
-          <a:ln>
-            <a:noFill/>
+          <a:ln w="19050">
+            <a:solidFill>
+              <a:schemeClr val="lt1"/>
+            </a:solidFill>
           </a:ln>
           <a:effectLst/>
         </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
         <c:dLbl>
           <c:idx val="0"/>
+          <c:layout/>
           <c:spPr>
             <a:noFill/>
             <a:ln>
@@ -1997,122 +2364,48 @@
             <a:effectLst/>
           </c:spPr>
           <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
               <a:spAutoFit/>
             </a:bodyPr>
             <a:lstStyle/>
             <a:p>
               <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                   <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
+                    <a:schemeClr val="bg1"/>
                   </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
+                  <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                   <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
+                  <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
                 </a:defRPr>
               </a:pPr>
-              <a:endParaRPr lang="en-US"/>
+              <a:endParaRPr lang="pt-BR"/>
             </a:p>
           </c:txPr>
           <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
+          <c:showVal val="1"/>
           <c:showCatName val="0"/>
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
           <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+              <c15:layout/>
+            </c:ext>
           </c:extLst>
         </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="4"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:srgbClr val="B5E6A2"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
-        <c:dLbl>
-          <c:idx val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-              <a:spAutoFit/>
-            </a:bodyPr>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="75000"/>
-                      <a:lumOff val="25000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
-          </c:extLst>
-        </c:dLbl>
-      </c:pivotFmt>
-      <c:pivotFmt>
-        <c:idx val="5"/>
-        <c:spPr>
-          <a:solidFill>
-            <a:schemeClr val="accent1"/>
-          </a:solidFill>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:marker>
-          <c:symbol val="none"/>
-        </c:marker>
       </c:pivotFmt>
     </c:pivotFmts>
     <c:plotArea>
       <c:layout/>
-      <c:barChart>
-        <c:barDir val="bar"/>
-        <c:grouping val="clustered"/>
-        <c:varyColors val="0"/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
         <c:ser>
           <c:idx val="0"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>C̳álculos!$D$4</c:f>
+              <c:f>C̳álculos!$D$33</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -2121,48 +2414,162 @@
               </c:strCache>
             </c:strRef>
           </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent1"/>
-            </a:solidFill>
-            <a:ln>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:tint val="65000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000001-96AA-4564-A7AE-205D46118A70}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000003-96AA-4564-A7AE-205D46118A70}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6">
+                  <a:shade val="65000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:ln w="19050">
+                <a:solidFill>
+                  <a:schemeClr val="lt1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:extLst>
+              <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                <c16:uniqueId val="{00000005-96AA-4564-A7AE-205D46118A70}"/>
+              </c:ext>
+            </c:extLst>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
               <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="bg1"/>
+                    </a:solidFill>
+                    <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="pt-BR"/>
+              </a:p>
+            </c:txPr>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="0"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
+              </c:ext>
+            </c:extLst>
+          </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>C̳álculos!$C$5:$C$7</c:f>
+              <c:f>C̳álculos!$C$34:$C$37</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>No</c:v>
+                  <c:v>Core</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>Yes</c:v>
+                  <c:v>Standard</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Ultimate</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>C̳álculos!$D$5:$D$7</c:f>
+              <c:f>C̳álculos!$D$34:$D$37</c:f>
               <c:numCache>
-                <c:formatCode>_-"R$"\ * #,##0.00_-;\-"R$"\ * #,##0.00_-;_-"R$"\ * "-"??_-;_-@_-</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>806</c:v>
+                  <c:v>28</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1502</c:v>
+                  <c:v>24</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>33</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-B6FB-45BD-B752-3282CC5F2BA3}"/>
+              <c16:uniqueId val="{00000006-96AA-4564-A7AE-205D46118A70}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2173,91 +2580,10 @@
           <c:showSerName val="0"/>
           <c:showPercent val="0"/>
           <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
         </c:dLbls>
-        <c:gapWidth val="182"/>
-        <c:axId val="1711244296"/>
-        <c:axId val="1711246344"/>
-      </c:barChart>
-      <c:catAx>
-        <c:axId val="1711244296"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1711246344"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1711246344"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="1"/>
-        <c:axPos val="b"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="_-&quot;R$&quot;\ * #,##0.00_-;\-&quot;R$&quot;\ * #,##0.00_-;_-&quot;R$&quot;\ * &quot;-&quot;??_-;_-@_-" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="1711244296"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
+        <c:firstSliceAng val="0"/>
+      </c:pieChart>
       <c:spPr>
         <a:noFill/>
         <a:ln>
@@ -2266,21 +2592,52 @@
         <a:effectLst/>
       </c:spPr>
     </c:plotArea>
+    <c:legend>
+      <c:legendPos val="l"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.14868683084404211"/>
+          <c:y val="0.38135884709284951"/>
+          <c:w val="0.11006732265844009"/>
+          <c:h val="0.23728230581430093"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="1"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1200" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="pt-BR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
     <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
+    <a:noFill/>
     <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
+      <a:noFill/>
       <a:round/>
     </a:ln>
     <a:effectLst/>
@@ -2290,20 +2647,27 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="pt-BR"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
     <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageMargins b="0.78740157499999996" l="0.511811024" r="0.511811024" t="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
     <c:pageSetup/>
   </c:printSettings>
   <c:extLst>
     <c:ext xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" uri="{781A3756-C4B2-4CAC-9D66-4F8BD8637D16}">
       <c14:pivotOptions>
-        <c14:dropZonesVisible val="1"/>
+        <c14:dropZoneFilter val="1"/>
+        <c14:dropZoneCategories val="1"/>
+        <c14:dropZoneData val="1"/>
+        <c14:dropZoneSeries val="1"/>
       </c14:pivotOptions>
     </c:ext>
     <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{E28EC0CA-F0BB-4C9C-879D-F8772B89E7AC}">
@@ -2356,42 +2720,8 @@
 </file>
 
 <file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="withinLinearReversed" id="26">
   <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
 </cs:colorStyle>
 </file>
 
@@ -2901,7 +3231,7 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="216">
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="251">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
     <cs:fillRef idx="0"/>
@@ -2958,7 +3288,7 @@
         <a:round/>
       </a:ln>
     </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
+    <cs:defRPr sz="900" kern="1200"/>
   </cs:chartArea>
   <cs:dataLabel>
     <cs:lnRef idx="0"/>
@@ -3009,6 +3339,13 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPoint>
   <cs:dataPoint3D>
     <cs:lnRef idx="0"/>
@@ -3019,12 +3356,19 @@
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
     </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="25400">
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
   </cs:dataPoint3D>
   <cs:dataPointLine>
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -3062,7 +3406,7 @@
     <cs:lnRef idx="0">
       <cs:styleClr val="auto"/>
     </cs:lnRef>
-    <cs:fillRef idx="1"/>
+    <cs:fillRef idx="0"/>
     <cs:effectRef idx="0"/>
     <cs:fontRef idx="minor">
       <a:schemeClr val="tx1"/>
@@ -3627,7 +3971,7 @@
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
           <a:extLst>
             <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-              <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId4"/>
+              <asvg:svgBlip xmlns="" xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId4"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -3861,8 +4205,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="1057275" y="5410199"/>
-          <a:ext cx="1549476" cy="752476"/>
+          <a:off x="1133475" y="5172074"/>
+          <a:ext cx="1778076" cy="714376"/>
           <a:chOff x="3495675" y="5400674"/>
           <a:chExt cx="1549476" cy="752476"/>
         </a:xfrm>
@@ -3919,7 +4263,7 @@
           <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9">
             <a:extLst>
               <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
-                <asvg:svgBlip xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId10"/>
+                <asvg:svgBlip xmlns="" xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId10"/>
               </a:ext>
             </a:extLst>
           </a:blip>
@@ -4142,100 +4486,85 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>981075</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>485775</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
-        <xdr:graphicFrame macro="">
-          <xdr:nvGraphicFramePr>
-            <xdr:cNvPr id="6" name="Subscription Type">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E1C3AB7F-7065-E65F-279A-E4366109F7F0}"/>
-                </a:ext>
-                <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-                  <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{97CFF8DB-D672-A498-570E-B6DE14CD0862}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvGraphicFramePr/>
-          </xdr:nvGraphicFramePr>
-          <xdr:xfrm>
-            <a:off x="0" y="0"/>
-            <a:ext cx="0" cy="0"/>
-          </xdr:xfrm>
-          <a:graphic>
-            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
-              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Subscription Type"/>
-            </a:graphicData>
-          </a:graphic>
-        </xdr:graphicFrame>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="0" name=""/>
-            <xdr:cNvSpPr>
-              <a:spLocks noTextEdit="1"/>
-            </xdr:cNvSpPr>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="2200275" y="1733550"/>
-              <a:ext cx="1828800" cy="1409700"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:prstClr val="white"/>
-            </a:solidFill>
-            <a:ln w="1">
-              <a:solidFill>
-                <a:prstClr val="green"/>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:endParaRPr sz="1100"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>223841</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>57151</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>411067</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>47624</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="Retângulo Arredondado 28"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2247904" y="6212682"/>
+          <a:ext cx="9938444" cy="4455317"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 5417"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="pt-BR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>266700</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:colOff>600074</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>128587</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>942975</xdr:colOff>
+      <xdr:colOff>1276349</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:rowOff>309563</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -4265,8 +4594,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="266700" y="104775"/>
-          <a:ext cx="676275" cy="676275"/>
+          <a:off x="600074" y="307181"/>
+          <a:ext cx="676275" cy="681038"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4275,31 +4604,863 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>88107</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1940718</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>152401</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+      <mc:Choice xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" Requires="a14">
+        <xdr:graphicFrame macro="">
+          <xdr:nvGraphicFramePr>
+            <xdr:cNvPr id="7" name="Subscription Type"/>
+            <xdr:cNvGraphicFramePr/>
+          </xdr:nvGraphicFramePr>
+          <xdr:xfrm>
+            <a:off x="0" y="0"/>
+            <a:ext cx="0" cy="0"/>
+          </xdr:xfrm>
+          <a:graphic>
+            <a:graphicData uri="http://schemas.microsoft.com/office/drawing/2010/slicer">
+              <sle:slicer xmlns:sle="http://schemas.microsoft.com/office/drawing/2010/slicer" name="Subscription Type"/>
+            </a:graphicData>
+          </a:graphic>
+        </xdr:graphicFrame>
+      </mc:Choice>
+      <mc:Fallback>
+        <xdr:sp macro="" textlink="">
+          <xdr:nvSpPr>
+            <xdr:cNvPr id="0" name=""/>
+            <xdr:cNvSpPr>
+              <a:spLocks noTextEdit="1"/>
+            </xdr:cNvSpPr>
+          </xdr:nvSpPr>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="0" y="2135982"/>
+              <a:ext cx="1940718" cy="1314450"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+            <a:solidFill>
+              <a:prstClr val="white"/>
+            </a:solidFill>
+            <a:ln w="1">
+              <a:solidFill>
+                <a:prstClr val="green"/>
+              </a:solidFill>
+            </a:ln>
+          </xdr:spPr>
+          <xdr:txBody>
+            <a:bodyPr vertOverflow="clip" horzOverflow="clip"/>
+            <a:lstStyle/>
+            <a:p>
+              <a:r>
+                <a:rPr lang="pt-BR" sz="1100"/>
+                <a:t>Esta forma representa uma segmentação de dados. Segmentações de dados têm suporte no Excel 2010 ou versões posteriores.
+\Se a forma tiver sido modificada em uma versão anterior do Excel, ou se a pasta de trabalho tiver sido salva no Excel 2003 ou versões anteriores, a segmentação de dados não poderá ser usada.</a:t>
+              </a:r>
+            </a:p>
+          </xdr:txBody>
+        </xdr:sp>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>297214</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="222565" cy="252185"/>
+    <xdr:sp macro="" textlink="D̳ashboard!$F$17">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="8" name="CaixaDeTexto 7"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3976245" y="2274094"/>
+          <a:ext cx="222565" cy="252185"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:fld id="{75E84242-EB67-48C1-86DF-88BDEAC29586}" type="TxLink">
+            <a:rPr lang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:srgbClr val="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Aptos Narrow"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:fld>
+          <a:endParaRPr lang="pt-BR" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>250031</xdr:colOff>
+      <xdr:row>4</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>488156</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>169069</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="15" name="Agrupar 14"/>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="2274094" y="1285875"/>
+          <a:ext cx="4655343" cy="1466850"/>
+          <a:chOff x="2274094" y="1285875"/>
+          <a:chExt cx="4655343" cy="1466850"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="3" name="Retângulo Arredondado 2"/>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="2297906" y="1297781"/>
+            <a:ext cx="4619625" cy="1345406"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst>
+              <a:gd name="adj" fmla="val 13127"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="pt-BR" sz="1100" b="1" cap="none" spc="0">
+              <a:ln w="22225">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="40000"/>
+                  <a:lumOff val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="C̳álculos!F17">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="9" name="Retângulo Arredondado 8"/>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="3831432" y="1797842"/>
+            <a:ext cx="3026570" cy="723899"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst>
+              <a:gd name="adj" fmla="val 13127"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:fld id="{A69ED993-B6B0-4888-ADEF-25B79E172AA0}" type="TxLink">
+              <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike" cap="none" spc="0">
+                <a:ln w="0">
+                  <a:noFill/>
+                </a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="5BF6A8"/>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:pPr algn="ctr"/>
+              <a:t> R$ 990,00 </a:t>
+            </a:fld>
+            <a:endParaRPr lang="en-US" sz="2800" b="1" cap="none" spc="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="5BF6A8"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="12" name="Imagem 11">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{34E653DD-5BBB-B7D9-BDBD-2F59393458E2}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill>
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+            <a:extLst>
+              <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              </a:ext>
+            </a:extLst>
+          </a:blip>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="3059905" y="1600200"/>
+            <a:ext cx="1371600" cy="1152525"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="13" name="Arredondar Retângulo no Mesmo Canto Lateral 12"/>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="2274094" y="1285875"/>
+            <a:ext cx="4655343" cy="452437"/>
+          </a:xfrm>
+          <a:prstGeom prst="round2SameRect">
+            <a:avLst>
+              <a:gd name="adj1" fmla="val 50000"/>
+              <a:gd name="adj2" fmla="val 0"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="2AE6B1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="pt-BR" sz="1200" b="1" baseline="0">
+                <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>TOTAL SUBSCRIPTIONS EA PLAY SEASON PASS</a:t>
+            </a:r>
+            <a:endParaRPr lang="pt-BR" sz="1100" b="1">
+              <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>307181</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>59531</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="24" name="Agrupar 23"/>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="7427119" y="1285875"/>
+          <a:ext cx="4655343" cy="1357312"/>
+          <a:chOff x="7427119" y="1285875"/>
+          <a:chExt cx="4655343" cy="1357312"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="17" name="Retângulo Arredondado 16"/>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="7450931" y="1297781"/>
+            <a:ext cx="4619625" cy="1345406"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst>
+              <a:gd name="adj" fmla="val 13127"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="pt-BR" sz="1100" b="1" cap="none" spc="0">
+              <a:ln w="22225">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="solid"/>
+              </a:ln>
+              <a:solidFill>
+                <a:schemeClr val="accent2">
+                  <a:lumMod val="40000"/>
+                  <a:lumOff val="60000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:effectLst/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="C̳álculos!F27">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="18" name="Retângulo Arredondado 17"/>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="8984457" y="1797842"/>
+            <a:ext cx="3026570" cy="723899"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst>
+              <a:gd name="adj" fmla="val 13127"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:fld id="{8E4AC87F-2FE2-49F2-8F90-6D1EB803B52C}" type="TxLink">
+              <a:rPr lang="en-US" sz="2800" b="1" i="0" u="none" strike="noStrike" cap="none" spc="0">
+                <a:ln w="0">
+                  <a:noFill/>
+                </a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="5BF6A8"/>
+                </a:solidFill>
+                <a:effectLst/>
+                <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t> R$ 1.140,00 </a:t>
+            </a:fld>
+            <a:endParaRPr lang="en-US" sz="6000" b="1" cap="none" spc="0">
+              <a:ln w="0">
+                <a:noFill/>
+              </a:ln>
+              <a:solidFill>
+                <a:srgbClr val="5BF6A8"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="20" name="Arredondar Retângulo no Mesmo Canto Lateral 19"/>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="7427119" y="1285875"/>
+            <a:ext cx="4655343" cy="452437"/>
+          </a:xfrm>
+          <a:prstGeom prst="round2SameRect">
+            <a:avLst>
+              <a:gd name="adj1" fmla="val 50000"/>
+              <a:gd name="adj2" fmla="val 0"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="2AE6B1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="pt-BR" sz="1200" b="1" baseline="0">
+                <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>TOTAL SUBSCRIPTIONS MINECRAFT SEASON PASS</a:t>
+            </a:r>
+            <a:endParaRPr lang="pt-BR" sz="1100" b="1">
+              <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:grpSp>
+        <xdr:nvGrpSpPr>
+          <xdr:cNvPr id="21" name="Agrupar 20">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A71E6AF1-ADEE-EB3B-0380-7B4EF5640C97}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvGrpSpPr/>
+        </xdr:nvGrpSpPr>
+        <xdr:grpSpPr>
+          <a:xfrm>
+            <a:off x="8048624" y="1893093"/>
+            <a:ext cx="1369219" cy="559595"/>
+            <a:chOff x="3495675" y="5400674"/>
+            <a:chExt cx="1549476" cy="752476"/>
+          </a:xfrm>
+        </xdr:grpSpPr>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="22" name="Imagem 21">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B0CF571B-D3D1-7AD8-F100-6A3A279BE54A}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3" cstate="print">
+              <a:extLst>
+                <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+                  <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+                </a:ext>
+              </a:extLst>
+            </a:blip>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3998608" y="5400674"/>
+              <a:ext cx="555497" cy="609599"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="23" name="Gráfico 13">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1F40A76-E1BB-A23E-B668-9F79247AB093}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr>
+              <a:picLocks noChangeAspect="1"/>
+            </xdr:cNvPicPr>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
+              <a:extLst>
+                <a:ext uri="{96DAC541-7B7A-43D3-8B79-37D633B846F1}">
+                  <asvg:svgBlip xmlns="" xmlns:asvg="http://schemas.microsoft.com/office/drawing/2016/SVG/main" r:embed="rId10"/>
+                </a:ext>
+              </a:extLst>
+            </a:blip>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="3495675" y="5895937"/>
+              <a:ext cx="1549476" cy="257213"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </xdr:grpSp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>200025</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>9524</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>440531</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>40481</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="27" name="Agrupar 26"/>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="2224088" y="2950368"/>
+          <a:ext cx="9991724" cy="2888457"/>
+          <a:chOff x="2224088" y="2950368"/>
+          <a:chExt cx="9991724" cy="2888457"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="4" name="Retângulo Arredondado 3"/>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="2238379" y="2976564"/>
+            <a:ext cx="9938444" cy="2857500"/>
+          </a:xfrm>
+          <a:prstGeom prst="roundRect">
+            <a:avLst>
+              <a:gd name="adj" fmla="val 5417"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:schemeClr val="bg1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="l"/>
+            <a:endParaRPr lang="pt-BR" sz="1100"/>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+      <xdr:graphicFrame macro="">
+        <xdr:nvGraphicFramePr>
+          <xdr:cNvPr id="5" name="Gráfico 4"/>
+          <xdr:cNvGraphicFramePr>
+            <a:graphicFrameLocks/>
+          </xdr:cNvGraphicFramePr>
+        </xdr:nvGraphicFramePr>
+        <xdr:xfrm>
+          <a:off x="2381250" y="3381375"/>
+          <a:ext cx="9572625" cy="2457450"/>
+        </xdr:xfrm>
+        <a:graphic>
+          <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+            <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
+          </a:graphicData>
+        </a:graphic>
+      </xdr:graphicFrame>
+      <xdr:sp macro="" textlink="">
+        <xdr:nvSpPr>
+          <xdr:cNvPr id="25" name="Arredondar Retângulo no Mesmo Canto Lateral 24"/>
+          <xdr:cNvSpPr/>
+        </xdr:nvSpPr>
+        <xdr:spPr>
+          <a:xfrm>
+            <a:off x="2224088" y="2950368"/>
+            <a:ext cx="9991724" cy="452437"/>
+          </a:xfrm>
+          <a:prstGeom prst="round2SameRect">
+            <a:avLst>
+              <a:gd name="adj1" fmla="val 50000"/>
+              <a:gd name="adj2" fmla="val 0"/>
+            </a:avLst>
+          </a:prstGeom>
+          <a:solidFill>
+            <a:srgbClr val="2AE6B1"/>
+          </a:solidFill>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="2">
+            <a:schemeClr val="accent1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:lnRef>
+          <a:fillRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="lt1"/>
+          </a:fontRef>
+        </xdr:style>
+        <xdr:txBody>
+          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr algn="ctr"/>
+            <a:r>
+              <a:rPr lang="pt-BR" sz="1200" b="1" baseline="0">
+                <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+                <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              </a:rPr>
+              <a:t>TOTAL SUBSCRIPTIONS XBOX GAME PASS</a:t>
+            </a:r>
+            <a:endParaRPr lang="pt-BR" sz="1100" b="1">
+              <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+            </a:endParaRPr>
+          </a:p>
+        </xdr:txBody>
+      </xdr:sp>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="absolute">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>488154</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>154781</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>250031</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>83344</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="3" name="Gráfico 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{772E5898-7783-409B-AB59-64039176D131}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{68D9E263-8317-4AF1-8B37-1DABBCEF3DFC}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
+        <xdr:cNvPr id="26" name="Gráfico 25"/>
         <xdr:cNvGraphicFramePr>
           <a:graphicFrameLocks/>
         </xdr:cNvGraphicFramePr>
@@ -4310,7 +5471,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -4318,50 +5479,82 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>30956</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>450056</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>126205</xdr:rowOff>
     </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="6" name="Gráfico 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C94CB5FB-348D-4F07-A8ED-8BD60977747E}"/>
-            </a:ext>
-            <a:ext uri="{147F2762-F138-4A5C-976F-8EAC2B608ADB}">
-              <a16:predDERef xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" pred="{772E5898-7783-409B-AB59-64039176D131}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr>
-          <a:graphicFrameLocks/>
-        </xdr:cNvGraphicFramePr>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="31" name="Arredondar Retângulo no Mesmo Canto Lateral 30"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2233613" y="6186487"/>
+          <a:ext cx="9991724" cy="452437"/>
+        </a:xfrm>
+        <a:prstGeom prst="round2SameRect">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 50000"/>
+            <a:gd name="adj2" fmla="val 0"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:srgbClr val="2AE6B1"/>
+        </a:solidFill>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1200" b="1" baseline="0">
+              <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+              <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+            </a:rPr>
+            <a:t>ACTIVE SUBSCRIPTIONS XBOX GAME PASS</a:t>
+          </a:r>
+          <a:endParaRPr lang="pt-BR" sz="1100" b="1">
+            <a:latin typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+            <a:cs typeface="Segoe UI" panose="020B0502040204020203" pitchFamily="34" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/pivotCache/pivotCacheDefinition1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" r:id="rId1" refreshedBy="Excel Services" refreshedDate="46067.912174884259" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="295" xr:uid="{F1237BB6-98D5-4B53-A809-B99C4085C21B}">
+<pivotCacheDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1" refreshedBy="Excel Services" refreshedDate="46067.912174884259" createdVersion="8" refreshedVersion="8" minRefreshableVersion="3" recordCount="295">
   <cacheSource type="worksheet">
     <worksheetSource name="Tabela1"/>
   </cacheSource>
@@ -4683,7 +5876,7 @@
         <s v="No"/>
       </sharedItems>
     </cacheField>
-    <cacheField name="Subscription Price" numFmtId="164">
+    <cacheField name="Subscription Price" numFmtId="44">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="5" maxValue="15"/>
     </cacheField>
     <cacheField name="Subscription Type" numFmtId="0">
@@ -4694,21 +5887,24 @@
       </sharedItems>
     </cacheField>
     <cacheField name="EA Play Season Pass" numFmtId="0">
-      <sharedItems/>
+      <sharedItems count="2">
+        <s v="Yes"/>
+        <s v="No"/>
+      </sharedItems>
     </cacheField>
-    <cacheField name="EA Play Season Pass_x000a_Price" numFmtId="164">
+    <cacheField name="EA Play Season Pass_x000a_Price" numFmtId="44">
       <sharedItems containsMixedTypes="1" containsNumber="1" containsInteger="1" minValue="30" maxValue="30"/>
     </cacheField>
     <cacheField name="Minecraft Season Pass" numFmtId="0">
       <sharedItems/>
     </cacheField>
-    <cacheField name="Minecraft Season Pass Price" numFmtId="164">
+    <cacheField name="Minecraft Season Pass Price" numFmtId="44">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="20"/>
     </cacheField>
-    <cacheField name="Coupon Value" numFmtId="164">
+    <cacheField name="Coupon Value" numFmtId="44">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="0" maxValue="20"/>
     </cacheField>
-    <cacheField name="Total Value" numFmtId="164">
+    <cacheField name="Total Value" numFmtId="44">
       <sharedItems containsSemiMixedTypes="0" containsString="0" containsNumber="1" containsInteger="1" minValue="3" maxValue="62" count="15">
         <n v="60"/>
         <n v="5"/>
@@ -4737,7 +5933,7 @@
 </file>
 
 <file path=xl/pivotCache/pivotCacheRecords1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" count="295">
+<pivotCacheRecords xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" count="295">
   <r>
     <n v="3231"/>
     <s v="João Silva"/>
@@ -4746,7 +5942,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -4761,7 +5957,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -4776,7 +5972,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -4791,7 +5987,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -4806,7 +6002,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -4821,7 +6017,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -4836,7 +6032,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="2"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -4851,7 +6047,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -4866,7 +6062,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -4881,7 +6077,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -4896,7 +6092,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -4911,7 +6107,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="1"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -4926,7 +6122,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -4941,7 +6137,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -4956,7 +6152,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -4971,7 +6167,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -4986,7 +6182,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -5001,7 +6197,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="2"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5016,7 +6212,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5031,7 +6227,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -5046,7 +6242,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5061,7 +6257,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5076,7 +6272,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -5091,7 +6287,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="1"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5106,7 +6302,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5121,7 +6317,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -5136,7 +6332,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5151,7 +6347,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5166,7 +6362,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -5181,7 +6377,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="2"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5196,7 +6392,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5211,7 +6407,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -5226,7 +6422,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5241,7 +6437,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5256,7 +6452,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -5271,7 +6467,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -5286,7 +6482,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="2"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5301,7 +6497,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5316,7 +6512,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -5331,7 +6527,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5346,7 +6542,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5361,7 +6557,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -5376,7 +6572,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="2"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5391,7 +6587,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5406,7 +6602,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -5421,7 +6617,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="1"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5436,7 +6632,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5451,7 +6647,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -5466,7 +6662,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5481,7 +6677,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5496,7 +6692,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -5511,7 +6707,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="2"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5526,7 +6722,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5541,7 +6737,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -5556,7 +6752,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5571,7 +6767,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5586,7 +6782,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -5601,7 +6797,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="1"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5616,7 +6812,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5631,7 +6827,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -5646,7 +6842,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5661,7 +6857,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5676,7 +6872,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -5691,7 +6887,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="2"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5706,7 +6902,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5721,7 +6917,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -5736,7 +6932,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="2"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5751,7 +6947,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5766,7 +6962,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -5781,7 +6977,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5796,7 +6992,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5811,7 +7007,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -5826,7 +7022,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="2"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5841,7 +7037,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5856,7 +7052,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -5871,7 +7067,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="1"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5886,7 +7082,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5901,7 +7097,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -5916,7 +7112,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5931,7 +7127,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5946,7 +7142,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -5961,7 +7157,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="2"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5976,7 +7172,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -5991,7 +7187,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -6006,7 +7202,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6021,7 +7217,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6036,7 +7232,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -6051,7 +7247,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="1"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6066,7 +7262,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6081,7 +7277,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -6096,7 +7292,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6111,7 +7307,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6126,7 +7322,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -6141,7 +7337,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="2"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6156,7 +7352,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6171,7 +7367,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -6186,7 +7382,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6201,7 +7397,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6216,7 +7412,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -6231,7 +7427,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6246,7 +7442,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6261,7 +7457,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -6276,7 +7472,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="2"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6291,7 +7487,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6306,7 +7502,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -6321,7 +7517,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -6336,7 +7532,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="2"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6351,7 +7547,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6366,7 +7562,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -6381,7 +7577,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6396,7 +7592,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6411,7 +7607,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -6426,7 +7622,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="2"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6441,7 +7637,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6456,7 +7652,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -6471,7 +7667,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="1"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6486,7 +7682,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6501,7 +7697,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -6516,7 +7712,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6531,7 +7727,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6546,7 +7742,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -6561,7 +7757,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="2"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6576,7 +7772,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6591,7 +7787,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -6606,7 +7802,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6621,7 +7817,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6636,7 +7832,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -6651,7 +7847,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="1"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6666,7 +7862,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6681,7 +7877,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -6696,7 +7892,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6711,7 +7907,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6726,7 +7922,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -6741,7 +7937,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="2"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6756,7 +7952,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6771,7 +7967,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -6786,7 +7982,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="2"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6801,7 +7997,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6816,7 +8012,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -6831,7 +8027,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6846,7 +8042,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6861,7 +8057,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -6876,7 +8072,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="2"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6891,7 +8087,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6906,7 +8102,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -6921,7 +8117,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="1"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6936,7 +8132,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6951,7 +8147,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -6966,7 +8162,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6981,7 +8177,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -6996,7 +8192,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -7011,7 +8207,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="2"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -7026,7 +8222,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -7041,7 +8237,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -7056,7 +8252,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -7071,7 +8267,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -7086,7 +8282,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -7101,7 +8297,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="1"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -7116,7 +8312,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -7131,7 +8327,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -7146,7 +8342,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -7161,7 +8357,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -7176,7 +8372,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -7191,7 +8387,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="2"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -7206,7 +8402,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -7221,7 +8417,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -7236,7 +8432,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -7251,7 +8447,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -7266,7 +8462,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -7281,7 +8477,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="1"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -7296,7 +8492,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -7311,7 +8507,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -7326,7 +8522,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -7341,7 +8537,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -7356,7 +8552,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -7371,7 +8567,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -7386,7 +8582,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="2"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -7401,7 +8597,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -7416,7 +8612,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -7431,7 +8627,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -7446,7 +8642,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -7461,7 +8657,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -7476,7 +8672,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="2"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -7491,7 +8687,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -7506,7 +8702,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -7521,7 +8717,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="1"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -7536,7 +8732,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -7551,7 +8747,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -7566,7 +8762,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -7581,7 +8777,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -7596,7 +8792,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -7611,7 +8807,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="2"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -7626,7 +8822,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -7641,7 +8837,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -7656,7 +8852,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -7671,7 +8867,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -7686,7 +8882,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -7701,7 +8897,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="1"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -7716,7 +8912,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -7731,7 +8927,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -7746,7 +8942,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -7761,7 +8957,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -7776,7 +8972,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -7791,7 +8987,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="2"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -7806,7 +9002,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -7821,7 +9017,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -7836,7 +9032,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="2"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -7851,7 +9047,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -7866,7 +9062,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -7881,7 +9077,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -7896,7 +9092,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -7911,7 +9107,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -7926,7 +9122,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="2"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -7941,7 +9137,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -7956,7 +9152,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -7971,7 +9167,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="1"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -7986,7 +9182,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8001,7 +9197,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -8016,7 +9212,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8031,7 +9227,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8046,7 +9242,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -8061,7 +9257,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="2"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8076,7 +9272,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8091,7 +9287,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -8106,7 +9302,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8121,7 +9317,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8136,7 +9332,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -8151,7 +9347,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="1"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8166,7 +9362,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8181,7 +9377,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -8196,7 +9392,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8211,7 +9407,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8226,7 +9422,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -8241,7 +9437,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="2"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8256,7 +9452,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8271,7 +9467,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -8286,7 +9482,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8301,7 +9497,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8316,7 +9512,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -8331,7 +9527,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="1"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8346,7 +9542,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8361,7 +9557,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -8376,7 +9572,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8391,7 +9587,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8406,7 +9602,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -8421,7 +9617,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="2"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8436,7 +9632,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8451,7 +9647,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -8466,7 +9662,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8481,7 +9677,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8496,7 +9692,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -8511,7 +9707,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="1"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8526,7 +9722,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8541,7 +9737,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -8556,7 +9752,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8571,7 +9767,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -8586,7 +9782,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="2"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8601,7 +9797,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8616,7 +9812,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -8631,7 +9827,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8646,7 +9842,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8661,7 +9857,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -8676,7 +9872,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="2"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8691,7 +9887,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8706,7 +9902,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -8721,7 +9917,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="1"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8736,7 +9932,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8751,7 +9947,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -8766,7 +9962,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8781,7 +9977,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8796,7 +9992,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -8811,7 +10007,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="2"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8826,7 +10022,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8841,7 +10037,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -8856,7 +10052,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8871,7 +10067,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8886,7 +10082,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -8901,7 +10097,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="1"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8916,7 +10112,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8931,7 +10127,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -8946,7 +10142,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8961,7 +10157,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -8976,7 +10172,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -8991,7 +10187,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="2"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -9006,7 +10202,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -9021,7 +10217,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -9036,7 +10232,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -9051,7 +10247,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -9066,7 +10262,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -9081,7 +10277,7 @@
     <x v="0"/>
     <n v="15"/>
     <x v="1"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -9096,7 +10292,7 @@
     <x v="1"/>
     <n v="10"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -9111,7 +10307,7 @@
     <x v="0"/>
     <n v="5"/>
     <x v="2"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -9126,7 +10322,7 @@
     <x v="1"/>
     <n v="15"/>
     <x v="0"/>
-    <s v="Yes"/>
+    <x v="0"/>
     <n v="30"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -9141,7 +10337,7 @@
     <x v="0"/>
     <n v="10"/>
     <x v="1"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="Yes"/>
     <n v="20"/>
@@ -9156,7 +10352,7 @@
     <x v="1"/>
     <n v="5"/>
     <x v="0"/>
-    <s v="No"/>
+    <x v="1"/>
     <s v="-"/>
     <s v="No"/>
     <n v="0"/>
@@ -9167,7 +10363,1251 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6C52E04D-F271-4F31-AF0F-C88034493B91}" name="Tabela dinâmica1" cacheId="402" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="22">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tabela dinâmica4" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="36">
+  <location ref="C33:D37" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="13">
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" numFmtId="14" outline="0" showAll="0">
+      <items count="295">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" numFmtId="44" outline="0" showAll="0"/>
+    <pivotField axis="axisPage" dataField="1" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="4">
+        <item h="1" x="1"/>
+        <item h="1" x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="44" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="44" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="44" outline="0" showAll="0">
+      <items count="16">
+        <item x="11"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="7"/>
+        <item x="10"/>
+        <item x="2"/>
+        <item x="13"/>
+        <item x="5"/>
+        <item x="8"/>
+        <item x="14"/>
+        <item x="6"/>
+        <item x="9"/>
+        <item x="12"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="6" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Contagem de Subscription Type" fld="6" subtotal="count" baseField="0" baseItem="0"/>
+  </dataFields>
+  <chartFormats count="5">
+    <chartFormat chart="32" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="35" format="12" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="35" format="13">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="35" format="14">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="1"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="35" format="15">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="2">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+          <reference field="2" count="1" selected="0">
+            <x v="2"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+  </chartFormats>
+  <pivotTableStyleInfo name="PivotStyleLight18" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tabela dinâmica3" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="32">
+  <location ref="C23:D27" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="13">
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" numFmtId="14" outline="0" showAll="0">
+      <items count="295">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" numFmtId="44" outline="0" showAll="0"/>
+    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="4">
+        <item h="1" x="1"/>
+        <item h="1" x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" numFmtId="44" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="44" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="44" outline="0" showAll="0">
+      <items count="16">
+        <item x="11"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="7"/>
+        <item x="10"/>
+        <item x="2"/>
+        <item x="13"/>
+        <item x="5"/>
+        <item x="8"/>
+        <item x="14"/>
+        <item x="6"/>
+        <item x="9"/>
+        <item x="12"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="6" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Soma de Minecraft Season Pass Price" fld="10" baseField="2" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight18" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tabela dinâmica2" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="32">
+  <location ref="C13:D17" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
+  <pivotFields count="13">
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField axis="axisRow" compact="0" outline="0" showAll="0">
+      <items count="4">
+        <item x="1"/>
+        <item x="2"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" numFmtId="14" outline="0" showAll="0">
+      <items count="295">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item x="3"/>
+        <item x="5"/>
+        <item x="6"/>
+        <item x="7"/>
+        <item x="4"/>
+        <item x="8"/>
+        <item x="9"/>
+        <item x="10"/>
+        <item x="11"/>
+        <item x="12"/>
+        <item x="13"/>
+        <item x="14"/>
+        <item x="15"/>
+        <item x="16"/>
+        <item x="17"/>
+        <item x="18"/>
+        <item x="19"/>
+        <item x="20"/>
+        <item x="21"/>
+        <item x="22"/>
+        <item x="23"/>
+        <item x="24"/>
+        <item x="25"/>
+        <item x="26"/>
+        <item x="27"/>
+        <item x="28"/>
+        <item x="29"/>
+        <item x="30"/>
+        <item x="31"/>
+        <item x="32"/>
+        <item x="33"/>
+        <item x="34"/>
+        <item x="35"/>
+        <item x="36"/>
+        <item x="37"/>
+        <item x="38"/>
+        <item x="39"/>
+        <item x="40"/>
+        <item x="41"/>
+        <item x="42"/>
+        <item x="43"/>
+        <item x="44"/>
+        <item x="45"/>
+        <item x="46"/>
+        <item x="47"/>
+        <item x="48"/>
+        <item x="49"/>
+        <item x="50"/>
+        <item x="51"/>
+        <item x="52"/>
+        <item x="53"/>
+        <item x="54"/>
+        <item x="55"/>
+        <item x="56"/>
+        <item x="57"/>
+        <item x="58"/>
+        <item x="59"/>
+        <item x="60"/>
+        <item x="61"/>
+        <item x="62"/>
+        <item x="63"/>
+        <item x="64"/>
+        <item x="65"/>
+        <item x="66"/>
+        <item x="67"/>
+        <item x="68"/>
+        <item x="69"/>
+        <item x="70"/>
+        <item x="71"/>
+        <item x="72"/>
+        <item x="73"/>
+        <item x="74"/>
+        <item x="75"/>
+        <item x="76"/>
+        <item x="77"/>
+        <item x="78"/>
+        <item x="79"/>
+        <item x="80"/>
+        <item x="81"/>
+        <item x="82"/>
+        <item x="83"/>
+        <item x="84"/>
+        <item x="85"/>
+        <item x="86"/>
+        <item x="87"/>
+        <item x="88"/>
+        <item x="89"/>
+        <item x="90"/>
+        <item x="91"/>
+        <item x="92"/>
+        <item x="93"/>
+        <item x="94"/>
+        <item x="95"/>
+        <item x="96"/>
+        <item x="97"/>
+        <item x="98"/>
+        <item x="99"/>
+        <item x="100"/>
+        <item x="101"/>
+        <item x="102"/>
+        <item x="103"/>
+        <item x="104"/>
+        <item x="105"/>
+        <item x="106"/>
+        <item x="107"/>
+        <item x="108"/>
+        <item x="109"/>
+        <item x="110"/>
+        <item x="111"/>
+        <item x="112"/>
+        <item x="113"/>
+        <item x="114"/>
+        <item x="115"/>
+        <item x="116"/>
+        <item x="117"/>
+        <item x="118"/>
+        <item x="119"/>
+        <item x="120"/>
+        <item x="121"/>
+        <item x="122"/>
+        <item x="123"/>
+        <item x="124"/>
+        <item x="125"/>
+        <item x="126"/>
+        <item x="127"/>
+        <item x="128"/>
+        <item x="129"/>
+        <item x="130"/>
+        <item x="131"/>
+        <item x="132"/>
+        <item x="133"/>
+        <item x="134"/>
+        <item x="135"/>
+        <item x="136"/>
+        <item x="137"/>
+        <item x="138"/>
+        <item x="139"/>
+        <item x="140"/>
+        <item x="141"/>
+        <item x="142"/>
+        <item x="143"/>
+        <item x="144"/>
+        <item x="145"/>
+        <item x="146"/>
+        <item x="147"/>
+        <item x="148"/>
+        <item x="149"/>
+        <item x="150"/>
+        <item x="151"/>
+        <item x="152"/>
+        <item x="153"/>
+        <item x="154"/>
+        <item x="155"/>
+        <item x="156"/>
+        <item x="157"/>
+        <item x="158"/>
+        <item x="159"/>
+        <item x="160"/>
+        <item x="161"/>
+        <item x="162"/>
+        <item x="163"/>
+        <item x="164"/>
+        <item x="165"/>
+        <item x="166"/>
+        <item x="167"/>
+        <item x="168"/>
+        <item x="169"/>
+        <item x="170"/>
+        <item x="171"/>
+        <item x="172"/>
+        <item x="173"/>
+        <item x="174"/>
+        <item x="175"/>
+        <item x="176"/>
+        <item x="177"/>
+        <item x="178"/>
+        <item x="179"/>
+        <item x="180"/>
+        <item x="181"/>
+        <item x="182"/>
+        <item x="183"/>
+        <item x="184"/>
+        <item x="185"/>
+        <item x="186"/>
+        <item x="187"/>
+        <item x="188"/>
+        <item x="189"/>
+        <item x="190"/>
+        <item x="191"/>
+        <item x="192"/>
+        <item x="193"/>
+        <item x="194"/>
+        <item x="195"/>
+        <item x="196"/>
+        <item x="197"/>
+        <item x="198"/>
+        <item x="199"/>
+        <item x="200"/>
+        <item x="201"/>
+        <item x="202"/>
+        <item x="203"/>
+        <item x="204"/>
+        <item x="205"/>
+        <item x="206"/>
+        <item x="207"/>
+        <item x="208"/>
+        <item x="209"/>
+        <item x="210"/>
+        <item x="211"/>
+        <item x="212"/>
+        <item x="213"/>
+        <item x="214"/>
+        <item x="215"/>
+        <item x="216"/>
+        <item x="217"/>
+        <item x="218"/>
+        <item x="219"/>
+        <item x="220"/>
+        <item x="221"/>
+        <item x="222"/>
+        <item x="223"/>
+        <item x="224"/>
+        <item x="225"/>
+        <item x="226"/>
+        <item x="227"/>
+        <item x="228"/>
+        <item x="229"/>
+        <item x="230"/>
+        <item x="231"/>
+        <item x="232"/>
+        <item x="233"/>
+        <item x="234"/>
+        <item x="235"/>
+        <item x="236"/>
+        <item x="237"/>
+        <item x="238"/>
+        <item x="239"/>
+        <item x="240"/>
+        <item x="241"/>
+        <item x="242"/>
+        <item x="243"/>
+        <item x="244"/>
+        <item x="245"/>
+        <item x="246"/>
+        <item x="247"/>
+        <item x="248"/>
+        <item x="249"/>
+        <item x="250"/>
+        <item x="251"/>
+        <item x="252"/>
+        <item x="253"/>
+        <item x="254"/>
+        <item x="255"/>
+        <item x="256"/>
+        <item x="257"/>
+        <item x="258"/>
+        <item x="259"/>
+        <item x="260"/>
+        <item x="261"/>
+        <item x="262"/>
+        <item x="263"/>
+        <item x="264"/>
+        <item x="265"/>
+        <item x="266"/>
+        <item x="267"/>
+        <item x="268"/>
+        <item x="269"/>
+        <item x="270"/>
+        <item x="271"/>
+        <item x="272"/>
+        <item x="273"/>
+        <item x="274"/>
+        <item x="275"/>
+        <item x="276"/>
+        <item x="277"/>
+        <item x="278"/>
+        <item x="279"/>
+        <item x="280"/>
+        <item x="281"/>
+        <item x="282"/>
+        <item x="283"/>
+        <item x="284"/>
+        <item x="285"/>
+        <item x="286"/>
+        <item x="287"/>
+        <item x="288"/>
+        <item x="289"/>
+        <item x="290"/>
+        <item x="291"/>
+        <item x="292"/>
+        <item x="293"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" numFmtId="44" outline="0" showAll="0"/>
+    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
+      <items count="4">
+        <item h="1" x="1"/>
+        <item h="1" x="0"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField compact="0" outline="0" showAll="0">
+      <items count="3">
+        <item x="1"/>
+        <item x="0"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="44" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="44" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="44" outline="0" showAll="0">
+      <items count="16">
+        <item x="11"/>
+        <item x="4"/>
+        <item x="1"/>
+        <item x="7"/>
+        <item x="10"/>
+        <item x="2"/>
+        <item x="13"/>
+        <item x="5"/>
+        <item x="8"/>
+        <item x="14"/>
+        <item x="6"/>
+        <item x="9"/>
+        <item x="12"/>
+        <item x="0"/>
+        <item x="3"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="2"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colItems count="1">
+    <i/>
+  </colItems>
+  <pageFields count="1">
+    <pageField fld="6" hier="-1"/>
+  </pageFields>
+  <dataFields count="1">
+    <dataField name="Soma de EA Play Season Pass" fld="8" baseField="2" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight18" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" name="Tabela dinâmica1" cacheId="2" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Valores" updatedVersion="6" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="35">
   <location ref="C4:D7" firstHeaderRow="1" firstDataRow="1" firstDataCol="1" rowPageCount="1" colPageCount="1"/>
   <pivotFields count="13">
     <pivotField compact="0" outline="0" showAll="0"/>
@@ -9495,21 +11935,21 @@
         </pivotArea>
       </autoSortScope>
     </pivotField>
-    <pivotField compact="0" numFmtId="164" outline="0" showAll="0"/>
-    <pivotField axis="axisPage" compact="0" outline="0" showAll="0">
+    <pivotField compact="0" numFmtId="44" outline="0" showAll="0"/>
+    <pivotField axis="axisPage" compact="0" outline="0" multipleItemSelectionAllowed="1" showAll="0">
       <items count="4">
         <item h="1" x="1"/>
-        <item x="0"/>
-        <item h="1" x="2"/>
+        <item h="1" x="0"/>
+        <item x="2"/>
         <item t="default"/>
       </items>
     </pivotField>
     <pivotField compact="0" outline="0" showAll="0"/>
     <pivotField compact="0" outline="0" showAll="0"/>
     <pivotField compact="0" outline="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="164" outline="0" showAll="0"/>
-    <pivotField compact="0" numFmtId="164" outline="0" showAll="0"/>
-    <pivotField dataField="1" compact="0" numFmtId="164" outline="0" showAll="0">
+    <pivotField compact="0" numFmtId="44" outline="0" showAll="0"/>
+    <pivotField compact="0" numFmtId="44" outline="0" showAll="0"/>
+    <pivotField dataField="1" compact="0" numFmtId="44" outline="0" showAll="0">
       <items count="16">
         <item x="11"/>
         <item x="4"/>
@@ -9548,12 +11988,12 @@
     <i/>
   </colItems>
   <pageFields count="1">
-    <pageField fld="6" item="2" hier="-1"/>
+    <pageField fld="6" hier="-1"/>
   </pageFields>
   <dataFields count="1">
-    <dataField name="Soma de Total Value" fld="12" baseField="0" baseItem="0" numFmtId="164"/>
+    <dataField name="Soma de Total Value" fld="12" baseField="0" baseItem="0" numFmtId="44"/>
   </dataFields>
-  <chartFormats count="4">
+  <chartFormats count="11">
     <chartFormat chart="8" format="1" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -9590,23 +12030,86 @@
         </references>
       </pivotArea>
     </chartFormat>
+    <chartFormat chart="11" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="17" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="28" format="0" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="31" format="4" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="32" format="5" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="33" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="34" format="6" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
   </chartFormats>
   <pivotTableStyleInfo name="PivotStyleLight18" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
       <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
     </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
   </extLst>
 </pivotTableDefinition>
 </file>
 
 <file path=xl/slicerCaches/slicerCache1.xml><?xml version="1.0" encoding="utf-8"?>
-<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10" name="SegmentaçãodeDados_Subscription_Type" xr10:uid="{E82B9B12-6AE1-4F25-ADA9-4E73AFF58177}" sourceName="Subscription Type">
+<slicerCacheDefinition xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x" name="SegmentaçãodeDados_Subscription_Type" sourceName="Subscription Type">
   <pivotTables>
     <pivotTable tabId="3" name="Tabela dinâmica1"/>
+    <pivotTable tabId="3" name="Tabela dinâmica2"/>
+    <pivotTable tabId="3" name="Tabela dinâmica3"/>
+    <pivotTable tabId="3" name="Tabela dinâmica4"/>
   </pivotTables>
   <data>
     <tabular pivotCacheId="1410655170">
@@ -9621,14 +12124,14 @@
 </file>
 
 <file path=xl/slicers/slicer1.xml><?xml version="1.0" encoding="utf-8"?>
-<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x xr10">
-  <slicer name="Subscription Type" xr10:uid="{EEE0A513-EC36-4235-A548-06FFEF59E7C6}" cache="SegmentaçãodeDados_Subscription_Type" caption="Subscription Type" rowHeight="228600"/>
+<slicers xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
+  <slicer name="Subscription Type" cache="SegmentaçãodeDados_Subscription_Type" caption="Subscription Type" style="XBOX" rowHeight="241300"/>
 </slicers>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{34E0E886-4200-4B36-97B3-63DB74FF40A0}" name="Tabela1" displayName="Tabela1" ref="A1:M296" totalsRowShown="0" dataDxfId="13">
-  <autoFilter ref="A1:M296" xr:uid="{34E0E886-4200-4B36-97B3-63DB74FF40A0}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabela1" displayName="Tabela1" ref="A1:M296" totalsRowShown="0" dataDxfId="16">
+  <autoFilter ref="A1:M296">
     <filterColumn colId="7">
       <filters>
         <filter val="Yes"/>
@@ -9636,21 +12139,43 @@
     </filterColumn>
   </autoFilter>
   <tableColumns count="13">
-    <tableColumn id="1" xr3:uid="{C4A90516-688A-46BF-9167-EA16C2A8A652}" name="Subscriber ID" dataDxfId="12"/>
-    <tableColumn id="2" xr3:uid="{53DD39D0-2220-4121-9E9D-4EAA7E151C0F}" name="Name" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{4F5FF271-4C57-4BE0-8F2C-F82C8551625C}" name="Plan" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{8C17EB93-79B9-4E55-B8F7-BEB82F8253E9}" name="Start Date" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{48CEDF9B-1689-482A-A828-5CCE7713264A}" name="Auto Renewal" dataDxfId="8"/>
-    <tableColumn id="6" xr3:uid="{78B82374-9AA7-4E38-AE4F-78CDE6C83720}" name="Subscription Price" dataDxfId="7" dataCellStyle="Moeda"/>
-    <tableColumn id="7" xr3:uid="{F2433F68-AF33-49D0-B1FB-19A396074EDE}" name="Subscription Type" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{FD4D9C95-F6E5-4933-9068-A71FF7DF9343}" name="EA Play Season Pass" dataDxfId="5"/>
-    <tableColumn id="13" xr3:uid="{978DD0D2-834E-4CE4-A39B-30976086932F}" name="EA Play Season Pass_x000a_Price" dataDxfId="4" dataCellStyle="Moeda"/>
-    <tableColumn id="9" xr3:uid="{6E29F111-C395-4580-9DAD-3407D9E8B1A4}" name="Minecraft Season Pass" dataDxfId="3"/>
-    <tableColumn id="10" xr3:uid="{EF544EAA-7F25-4FD5-A10E-8E62804DB9E3}" name="Minecraft Season Pass Price" dataDxfId="2" dataCellStyle="Moeda"/>
-    <tableColumn id="11" xr3:uid="{7F6EB64A-1F07-4E48-9F0F-AC7D9DCD26F8}" name="Coupon Value" dataDxfId="1" dataCellStyle="Moeda"/>
-    <tableColumn id="12" xr3:uid="{2B04ABC8-DE6F-426E-ADC0-D8AFC68CA58E}" name="Total Value" dataDxfId="0" dataCellStyle="Moeda"/>
+    <tableColumn id="1" name="Subscriber ID" dataDxfId="15"/>
+    <tableColumn id="2" name="Name" dataDxfId="14"/>
+    <tableColumn id="3" name="Plan" dataDxfId="13"/>
+    <tableColumn id="4" name="Start Date" dataDxfId="12"/>
+    <tableColumn id="5" name="Auto Renewal" dataDxfId="11"/>
+    <tableColumn id="6" name="Subscription Price" dataDxfId="10" dataCellStyle="Moeda"/>
+    <tableColumn id="7" name="Subscription Type" dataDxfId="9"/>
+    <tableColumn id="8" name="EA Play Season Pass" dataDxfId="8"/>
+    <tableColumn id="13" name="EA Play Season Pass_x000a_Price" dataDxfId="7" dataCellStyle="Moeda"/>
+    <tableColumn id="9" name="Minecraft Season Pass" dataDxfId="6"/>
+    <tableColumn id="10" name="Minecraft Season Pass Price" dataDxfId="5" dataCellStyle="Moeda"/>
+    <tableColumn id="11" name="Coupon Value" dataDxfId="4" dataCellStyle="Moeda"/>
+    <tableColumn id="12" name="Total Value" dataDxfId="3" dataCellStyle="Moeda"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight11" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="Tabela2" displayName="Tabela2" ref="A1:M25" totalsRowShown="0">
+  <autoFilter ref="A1:M25"/>
+  <tableColumns count="13">
+    <tableColumn id="1" name="Subscriber ID"/>
+    <tableColumn id="2" name="Name"/>
+    <tableColumn id="3" name="Plan"/>
+    <tableColumn id="4" name="Start Date" dataDxfId="0"/>
+    <tableColumn id="5" name="Auto Renewal"/>
+    <tableColumn id="6" name="Subscription Price"/>
+    <tableColumn id="7" name="Subscription Type"/>
+    <tableColumn id="8" name="EA Play Season Pass"/>
+    <tableColumn id="9" name="EA Play Season Pass_x000a_Price"/>
+    <tableColumn id="10" name="Minecraft Season Pass"/>
+    <tableColumn id="11" name="Minecraft Season Pass Price"/>
+    <tableColumn id="12" name="Coupon Value"/>
+    <tableColumn id="13" name="Total Value"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -9970,14 +12495,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F18745-D22C-475B-A007-B964F001EBFB}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="3" tint="0.749992370372631"/>
   </sheetPr>
   <dimension ref="B3:P21"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="9" max="9" width="3.5703125" customWidth="1"/>
+    <col min="9" max="9" width="3.625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="2:16" ht="20.25" thickBot="1">
@@ -9991,7 +12516,7 @@
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
     </row>
-    <row r="4" spans="2:16" ht="15.75" thickTop="1"/>
+    <row r="4" spans="2:16" ht="15" thickTop="1"/>
     <row r="5" spans="2:16">
       <c r="B5" s="3" t="s">
         <v>1</v>
@@ -10050,7 +12575,7 @@
       <c r="O12" s="1"/>
       <c r="P12" s="1"/>
     </row>
-    <row r="13" spans="2:16" ht="15.75" thickTop="1">
+    <row r="13" spans="2:16" ht="15" thickTop="1">
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
@@ -10138,26 +12663,26 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56040718-600F-40D2-9E7A-13AED8C24C13}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="3" tint="0.749992370372631"/>
   </sheetPr>
   <dimension ref="A1:M296"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="18.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.5" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="22" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="20.5703125" customWidth="1"/>
-    <col min="10" max="10" width="16.7109375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="21.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="20.625" customWidth="1"/>
+    <col min="10" max="10" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="21.25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="30">
@@ -22306,24 +24831,1077 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BF79518-957B-4D6A-A3ED-CC74AA9E1C81}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="3" tint="0.749992370372631"/>
   </sheetPr>
-  <dimension ref="C2:D7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:M25"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
-    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="18.7109375" customWidth="1"/>
+    <col min="1" max="1" width="14.875" customWidth="1"/>
+    <col min="4" max="4" width="11.625" customWidth="1"/>
+    <col min="5" max="5" width="14.875" customWidth="1"/>
+    <col min="6" max="6" width="19.125" customWidth="1"/>
+    <col min="7" max="7" width="18.875" customWidth="1"/>
+    <col min="8" max="8" width="21.125" customWidth="1"/>
+    <col min="10" max="10" width="23" customWidth="1"/>
+    <col min="11" max="11" width="28.125" customWidth="1"/>
+    <col min="12" max="12" width="15.125" customWidth="1"/>
+    <col min="13" max="13" width="12.625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13">
+      <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" t="s">
+        <v>16</v>
+      </c>
+      <c r="G1" t="s">
+        <v>17</v>
+      </c>
+      <c r="H1" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2">
+        <v>3518</v>
+      </c>
+      <c r="B2" t="s">
+        <v>305</v>
+      </c>
+      <c r="C2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="18">
+        <v>45635</v>
+      </c>
+      <c r="E2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F2">
+        <v>10</v>
+      </c>
+      <c r="G2" t="s">
+        <v>35</v>
+      </c>
+      <c r="H2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" t="s">
+        <v>32</v>
+      </c>
+      <c r="J2" t="s">
+        <v>26</v>
+      </c>
+      <c r="K2">
+        <v>20</v>
+      </c>
+      <c r="L2">
+        <v>12</v>
+      </c>
+      <c r="M2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3">
+        <v>3506</v>
+      </c>
+      <c r="B3" t="s">
+        <v>296</v>
+      </c>
+      <c r="C3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="18">
+        <v>45623</v>
+      </c>
+      <c r="E3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F3">
+        <v>10</v>
+      </c>
+      <c r="G3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" t="s">
+        <v>32</v>
+      </c>
+      <c r="J3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K3">
+        <v>20</v>
+      </c>
+      <c r="L3">
+        <v>15</v>
+      </c>
+      <c r="M3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4">
+        <v>3233</v>
+      </c>
+      <c r="B4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="18">
+        <v>45332</v>
+      </c>
+      <c r="E4" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4">
+        <v>10</v>
+      </c>
+      <c r="G4" t="s">
+        <v>35</v>
+      </c>
+      <c r="H4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" t="s">
+        <v>32</v>
+      </c>
+      <c r="J4" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4">
+        <v>20</v>
+      </c>
+      <c r="L4">
+        <v>10</v>
+      </c>
+      <c r="M4">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5">
+        <v>3494</v>
+      </c>
+      <c r="B5" t="s">
+        <v>285</v>
+      </c>
+      <c r="C5" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="18">
+        <v>45611</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5">
+        <v>10</v>
+      </c>
+      <c r="G5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H5" t="s">
+        <v>30</v>
+      </c>
+      <c r="I5" t="s">
+        <v>32</v>
+      </c>
+      <c r="J5" t="s">
+        <v>26</v>
+      </c>
+      <c r="K5">
+        <v>20</v>
+      </c>
+      <c r="L5">
+        <v>12</v>
+      </c>
+      <c r="M5">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6">
+        <v>3480</v>
+      </c>
+      <c r="B6" t="s">
+        <v>271</v>
+      </c>
+      <c r="C6" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="18">
+        <v>45597</v>
+      </c>
+      <c r="E6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6">
+        <v>10</v>
+      </c>
+      <c r="G6" t="s">
+        <v>35</v>
+      </c>
+      <c r="H6" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" t="s">
+        <v>32</v>
+      </c>
+      <c r="J6" t="s">
+        <v>26</v>
+      </c>
+      <c r="K6">
+        <v>20</v>
+      </c>
+      <c r="L6">
+        <v>15</v>
+      </c>
+      <c r="M6">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7">
+        <v>3468</v>
+      </c>
+      <c r="B7" t="s">
+        <v>260</v>
+      </c>
+      <c r="C7" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="18">
+        <v>45585</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7">
+        <v>10</v>
+      </c>
+      <c r="G7" t="s">
+        <v>35</v>
+      </c>
+      <c r="H7" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" t="s">
+        <v>32</v>
+      </c>
+      <c r="J7" t="s">
+        <v>26</v>
+      </c>
+      <c r="K7">
+        <v>20</v>
+      </c>
+      <c r="L7">
+        <v>12</v>
+      </c>
+      <c r="M7">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8">
+        <v>3456</v>
+      </c>
+      <c r="B8" t="s">
+        <v>249</v>
+      </c>
+      <c r="C8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="18">
+        <v>45573</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8">
+        <v>10</v>
+      </c>
+      <c r="G8" t="s">
+        <v>35</v>
+      </c>
+      <c r="H8" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" t="s">
+        <v>32</v>
+      </c>
+      <c r="J8" t="s">
+        <v>26</v>
+      </c>
+      <c r="K8">
+        <v>20</v>
+      </c>
+      <c r="L8">
+        <v>15</v>
+      </c>
+      <c r="M8">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9">
+        <v>3444</v>
+      </c>
+      <c r="B9" t="s">
+        <v>240</v>
+      </c>
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+      <c r="D9" s="18">
+        <v>45561</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9">
+        <v>10</v>
+      </c>
+      <c r="G9" t="s">
+        <v>35</v>
+      </c>
+      <c r="H9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" t="s">
+        <v>32</v>
+      </c>
+      <c r="J9" t="s">
+        <v>26</v>
+      </c>
+      <c r="K9">
+        <v>20</v>
+      </c>
+      <c r="L9">
+        <v>12</v>
+      </c>
+      <c r="M9">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10">
+        <v>3426</v>
+      </c>
+      <c r="B10" t="s">
+        <v>200</v>
+      </c>
+      <c r="C10" t="s">
+        <v>34</v>
+      </c>
+      <c r="D10" s="18">
+        <v>45543</v>
+      </c>
+      <c r="E10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10">
+        <v>10</v>
+      </c>
+      <c r="G10" t="s">
+        <v>35</v>
+      </c>
+      <c r="H10" t="s">
+        <v>30</v>
+      </c>
+      <c r="I10" t="s">
+        <v>32</v>
+      </c>
+      <c r="J10" t="s">
+        <v>26</v>
+      </c>
+      <c r="K10">
+        <v>20</v>
+      </c>
+      <c r="L10">
+        <v>15</v>
+      </c>
+      <c r="M10">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11">
+        <v>3240</v>
+      </c>
+      <c r="B11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" t="s">
+        <v>34</v>
+      </c>
+      <c r="D11" s="18">
+        <v>45357</v>
+      </c>
+      <c r="E11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11">
+        <v>10</v>
+      </c>
+      <c r="G11" t="s">
+        <v>35</v>
+      </c>
+      <c r="H11" t="s">
+        <v>30</v>
+      </c>
+      <c r="I11" t="s">
+        <v>32</v>
+      </c>
+      <c r="J11" t="s">
+        <v>26</v>
+      </c>
+      <c r="K11">
+        <v>20</v>
+      </c>
+      <c r="L11">
+        <v>15</v>
+      </c>
+      <c r="M11">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12">
+        <v>3414</v>
+      </c>
+      <c r="B12" t="s">
+        <v>213</v>
+      </c>
+      <c r="C12" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="18">
+        <v>45531</v>
+      </c>
+      <c r="E12" t="s">
+        <v>26</v>
+      </c>
+      <c r="F12">
+        <v>10</v>
+      </c>
+      <c r="G12" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" t="s">
+        <v>30</v>
+      </c>
+      <c r="I12" t="s">
+        <v>32</v>
+      </c>
+      <c r="J12" t="s">
+        <v>26</v>
+      </c>
+      <c r="K12">
+        <v>20</v>
+      </c>
+      <c r="L12">
+        <v>12</v>
+      </c>
+      <c r="M12">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13">
+        <v>3398</v>
+      </c>
+      <c r="B13" t="s">
+        <v>197</v>
+      </c>
+      <c r="C13" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="18">
+        <v>45515</v>
+      </c>
+      <c r="E13" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13">
+        <v>10</v>
+      </c>
+      <c r="G13" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13" t="s">
+        <v>30</v>
+      </c>
+      <c r="I13" t="s">
+        <v>32</v>
+      </c>
+      <c r="J13" t="s">
+        <v>26</v>
+      </c>
+      <c r="K13">
+        <v>20</v>
+      </c>
+      <c r="L13">
+        <v>15</v>
+      </c>
+      <c r="M13">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14">
+        <v>3386</v>
+      </c>
+      <c r="B14" t="s">
+        <v>187</v>
+      </c>
+      <c r="C14" t="s">
+        <v>34</v>
+      </c>
+      <c r="D14" s="18">
+        <v>45503</v>
+      </c>
+      <c r="E14" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14">
+        <v>10</v>
+      </c>
+      <c r="G14" t="s">
+        <v>35</v>
+      </c>
+      <c r="H14" t="s">
+        <v>30</v>
+      </c>
+      <c r="I14" t="s">
+        <v>32</v>
+      </c>
+      <c r="J14" t="s">
+        <v>26</v>
+      </c>
+      <c r="K14">
+        <v>20</v>
+      </c>
+      <c r="L14">
+        <v>15</v>
+      </c>
+      <c r="M14">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15">
+        <v>3374</v>
+      </c>
+      <c r="B15" t="s">
+        <v>175</v>
+      </c>
+      <c r="C15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="18">
+        <v>45491</v>
+      </c>
+      <c r="E15" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15">
+        <v>10</v>
+      </c>
+      <c r="G15" t="s">
+        <v>35</v>
+      </c>
+      <c r="H15" t="s">
+        <v>30</v>
+      </c>
+      <c r="I15" t="s">
+        <v>32</v>
+      </c>
+      <c r="J15" t="s">
+        <v>26</v>
+      </c>
+      <c r="K15">
+        <v>20</v>
+      </c>
+      <c r="L15">
+        <v>12</v>
+      </c>
+      <c r="M15">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
+      <c r="A16">
+        <v>3356</v>
+      </c>
+      <c r="B16" t="s">
+        <v>157</v>
+      </c>
+      <c r="C16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D16" s="18">
+        <v>45473</v>
+      </c>
+      <c r="E16" t="s">
+        <v>26</v>
+      </c>
+      <c r="F16">
+        <v>10</v>
+      </c>
+      <c r="G16" t="s">
+        <v>35</v>
+      </c>
+      <c r="H16" t="s">
+        <v>30</v>
+      </c>
+      <c r="I16" t="s">
+        <v>32</v>
+      </c>
+      <c r="J16" t="s">
+        <v>26</v>
+      </c>
+      <c r="K16">
+        <v>20</v>
+      </c>
+      <c r="L16">
+        <v>15</v>
+      </c>
+      <c r="M16">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
+      <c r="A17">
+        <v>3344</v>
+      </c>
+      <c r="B17" t="s">
+        <v>146</v>
+      </c>
+      <c r="C17" t="s">
+        <v>34</v>
+      </c>
+      <c r="D17" s="18">
+        <v>45461</v>
+      </c>
+      <c r="E17" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17">
+        <v>10</v>
+      </c>
+      <c r="G17" t="s">
+        <v>35</v>
+      </c>
+      <c r="H17" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17" t="s">
+        <v>32</v>
+      </c>
+      <c r="J17" t="s">
+        <v>26</v>
+      </c>
+      <c r="K17">
+        <v>20</v>
+      </c>
+      <c r="L17">
+        <v>12</v>
+      </c>
+      <c r="M17">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
+      <c r="A18">
+        <v>3334</v>
+      </c>
+      <c r="B18" t="s">
+        <v>136</v>
+      </c>
+      <c r="C18" t="s">
+        <v>34</v>
+      </c>
+      <c r="D18" s="18">
+        <v>45451</v>
+      </c>
+      <c r="E18" t="s">
+        <v>30</v>
+      </c>
+      <c r="F18">
+        <v>10</v>
+      </c>
+      <c r="G18" t="s">
+        <v>35</v>
+      </c>
+      <c r="H18" t="s">
+        <v>30</v>
+      </c>
+      <c r="I18" t="s">
+        <v>32</v>
+      </c>
+      <c r="J18" t="s">
+        <v>26</v>
+      </c>
+      <c r="K18">
+        <v>20</v>
+      </c>
+      <c r="L18">
+        <v>12</v>
+      </c>
+      <c r="M18">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
+      <c r="A19">
+        <v>3325</v>
+      </c>
+      <c r="B19" t="s">
+        <v>127</v>
+      </c>
+      <c r="C19" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="18">
+        <v>45442</v>
+      </c>
+      <c r="E19" t="s">
+        <v>26</v>
+      </c>
+      <c r="F19">
+        <v>10</v>
+      </c>
+      <c r="G19" t="s">
+        <v>35</v>
+      </c>
+      <c r="H19" t="s">
+        <v>30</v>
+      </c>
+      <c r="I19" t="s">
+        <v>32</v>
+      </c>
+      <c r="J19" t="s">
+        <v>26</v>
+      </c>
+      <c r="K19">
+        <v>20</v>
+      </c>
+      <c r="L19">
+        <v>15</v>
+      </c>
+      <c r="M19">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
+      <c r="A20">
+        <v>3316</v>
+      </c>
+      <c r="B20" t="s">
+        <v>118</v>
+      </c>
+      <c r="C20" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" s="18">
+        <v>45433</v>
+      </c>
+      <c r="E20" t="s">
+        <v>30</v>
+      </c>
+      <c r="F20">
+        <v>10</v>
+      </c>
+      <c r="G20" t="s">
+        <v>35</v>
+      </c>
+      <c r="H20" t="s">
+        <v>30</v>
+      </c>
+      <c r="I20" t="s">
+        <v>32</v>
+      </c>
+      <c r="J20" t="s">
+        <v>26</v>
+      </c>
+      <c r="K20">
+        <v>20</v>
+      </c>
+      <c r="L20">
+        <v>15</v>
+      </c>
+      <c r="M20">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
+      <c r="A21">
+        <v>3304</v>
+      </c>
+      <c r="B21" t="s">
+        <v>106</v>
+      </c>
+      <c r="C21" t="s">
+        <v>34</v>
+      </c>
+      <c r="D21" s="18">
+        <v>45421</v>
+      </c>
+      <c r="E21" t="s">
+        <v>30</v>
+      </c>
+      <c r="F21">
+        <v>10</v>
+      </c>
+      <c r="G21" t="s">
+        <v>35</v>
+      </c>
+      <c r="H21" t="s">
+        <v>30</v>
+      </c>
+      <c r="I21" t="s">
+        <v>32</v>
+      </c>
+      <c r="J21" t="s">
+        <v>26</v>
+      </c>
+      <c r="K21">
+        <v>20</v>
+      </c>
+      <c r="L21">
+        <v>12</v>
+      </c>
+      <c r="M21">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
+      <c r="A22">
+        <v>3286</v>
+      </c>
+      <c r="B22" t="s">
+        <v>88</v>
+      </c>
+      <c r="C22" t="s">
+        <v>34</v>
+      </c>
+      <c r="D22" s="18">
+        <v>45403</v>
+      </c>
+      <c r="E22" t="s">
+        <v>26</v>
+      </c>
+      <c r="F22">
+        <v>10</v>
+      </c>
+      <c r="G22" t="s">
+        <v>35</v>
+      </c>
+      <c r="H22" t="s">
+        <v>30</v>
+      </c>
+      <c r="I22" t="s">
+        <v>32</v>
+      </c>
+      <c r="J22" t="s">
+        <v>26</v>
+      </c>
+      <c r="K22">
+        <v>20</v>
+      </c>
+      <c r="L22">
+        <v>15</v>
+      </c>
+      <c r="M22">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
+      <c r="A23">
+        <v>3252</v>
+      </c>
+      <c r="B23" t="s">
+        <v>54</v>
+      </c>
+      <c r="C23" t="s">
+        <v>34</v>
+      </c>
+      <c r="D23" s="18">
+        <v>45369</v>
+      </c>
+      <c r="E23" t="s">
+        <v>26</v>
+      </c>
+      <c r="F23">
+        <v>10</v>
+      </c>
+      <c r="G23" t="s">
+        <v>35</v>
+      </c>
+      <c r="H23" t="s">
+        <v>30</v>
+      </c>
+      <c r="I23" t="s">
+        <v>32</v>
+      </c>
+      <c r="J23" t="s">
+        <v>26</v>
+      </c>
+      <c r="K23">
+        <v>20</v>
+      </c>
+      <c r="L23">
+        <v>15</v>
+      </c>
+      <c r="M23">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
+      <c r="A24">
+        <v>3274</v>
+      </c>
+      <c r="B24" t="s">
+        <v>76</v>
+      </c>
+      <c r="C24" t="s">
+        <v>34</v>
+      </c>
+      <c r="D24" s="18">
+        <v>45391</v>
+      </c>
+      <c r="E24" t="s">
+        <v>26</v>
+      </c>
+      <c r="F24">
+        <v>10</v>
+      </c>
+      <c r="G24" t="s">
+        <v>35</v>
+      </c>
+      <c r="H24" t="s">
+        <v>30</v>
+      </c>
+      <c r="I24" t="s">
+        <v>32</v>
+      </c>
+      <c r="J24" t="s">
+        <v>26</v>
+      </c>
+      <c r="K24">
+        <v>20</v>
+      </c>
+      <c r="L24">
+        <v>12</v>
+      </c>
+      <c r="M24">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
+      <c r="A25">
+        <v>3264</v>
+      </c>
+      <c r="B25" t="s">
+        <v>66</v>
+      </c>
+      <c r="C25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="18">
+        <v>45381</v>
+      </c>
+      <c r="E25" t="s">
+        <v>26</v>
+      </c>
+      <c r="F25">
+        <v>10</v>
+      </c>
+      <c r="G25" t="s">
+        <v>35</v>
+      </c>
+      <c r="H25" t="s">
+        <v>30</v>
+      </c>
+      <c r="I25" t="s">
+        <v>32</v>
+      </c>
+      <c r="J25" t="s">
+        <v>26</v>
+      </c>
+      <c r="K25">
+        <v>20</v>
+      </c>
+      <c r="L25">
+        <v>15</v>
+      </c>
+      <c r="M25">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="3" tint="0.749992370372631"/>
+  </sheetPr>
+  <dimension ref="C2:F37"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
+  <cols>
+    <col min="3" max="3" width="15.625" customWidth="1"/>
+    <col min="4" max="4" width="29.875" customWidth="1"/>
+    <col min="5" max="5" width="27.875" customWidth="1"/>
     <col min="6" max="7" width="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.28515625" customWidth="1"/>
-    <col min="9" max="10" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="10.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.25" customWidth="1"/>
+    <col min="9" max="10" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.25" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="9.25" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="10.25" bestFit="1" customWidth="1"/>
     <col min="18" max="19" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -22367,29 +25945,175 @@
         <v>2308</v>
       </c>
     </row>
+    <row r="11" spans="3:4">
+      <c r="C11" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D11" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="3:4">
+      <c r="C13" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="14" spans="3:4">
+      <c r="C14" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="3:4">
+      <c r="C15" t="s">
+        <v>34</v>
+      </c>
+      <c r="D15" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="3:4">
+      <c r="C16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="16">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="17" spans="3:6">
+      <c r="C17" t="s">
+        <v>314</v>
+      </c>
+      <c r="D17" s="16">
+        <v>990</v>
+      </c>
+      <c r="F17" s="17">
+        <f>GETPIVOTDATA("EA Play Season Pass
+Price",$C$13)</f>
+        <v>990</v>
+      </c>
+    </row>
+    <row r="21" spans="3:6">
+      <c r="C21" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D21" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="3:6">
+      <c r="C23" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D23" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="24" spans="3:6">
+      <c r="C24" t="s">
+        <v>29</v>
+      </c>
+      <c r="D24" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:6">
+      <c r="C25" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="16">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="26" spans="3:6">
+      <c r="C26" t="s">
+        <v>25</v>
+      </c>
+      <c r="D26" s="16">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="27" spans="3:6">
+      <c r="C27" t="s">
+        <v>314</v>
+      </c>
+      <c r="D27" s="16">
+        <v>1140</v>
+      </c>
+      <c r="F27" s="17">
+        <f>GETPIVOTDATA("Minecraft Season Pass Price",$C$23)</f>
+        <v>1140</v>
+      </c>
+    </row>
+    <row r="31" spans="3:6">
+      <c r="C31" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D31" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="33" spans="3:4">
+      <c r="C33" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D33" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="34" spans="3:4">
+      <c r="C34" t="s">
+        <v>29</v>
+      </c>
+      <c r="D34" s="16">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="35" spans="3:4">
+      <c r="C35" t="s">
+        <v>34</v>
+      </c>
+      <c r="D35" s="16">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="36" spans="3:4">
+      <c r="C36" t="s">
+        <v>25</v>
+      </c>
+      <c r="D36" s="16">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="37" spans="3:4">
+      <c r="C37" t="s">
+        <v>314</v>
+      </c>
+      <c r="D37" s="16">
+        <v>85</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
-  <drawing r:id="rId2"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
-      <x14:slicerList>
-        <x14:slicer r:id="rId3"/>
-      </x14:slicerList>
-    </ext>
-  </extLst>
+  <drawing r:id="rId5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{210F14EF-C0B7-459D-9E09-3130BA4314A6}">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:Q8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="20" style="5" customWidth="1"/>
-    <col min="2" max="2" width="3.5703125" style="7" customWidth="1"/>
-    <col min="3" max="11" width="9.140625" style="7"/>
-    <col min="12" max="12" width="6.5703125" style="7" customWidth="1"/>
-    <col min="13" max="16384" width="9.140625" style="7"/>
+    <col min="1" max="1" width="26.625" style="5" customWidth="1"/>
+    <col min="2" max="2" width="3.625" style="7" customWidth="1"/>
+    <col min="3" max="11" width="9.125" style="7"/>
+    <col min="12" max="12" width="6.625" style="7" customWidth="1"/>
+    <col min="13" max="16384" width="9.125" style="7"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" customFormat="1">
@@ -22427,18 +26151,23 @@
   </sheetData>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <drawing r:id="rId1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{A8765BA9-456A-4dab-B4F3-ACF838C121DE}">
+      <x14:slicerList>
+        <x14:slicer r:id="rId2"/>
+      </x14:slicerList>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="851b35d3-0456-4d6a-bc2f-da927e91d158">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="19483571-f922-4e8e-9c1c-26f0a2252132" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -22697,22 +26426,57 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="851b35d3-0456-4d6a-bc2f-da927e91d158">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="19483571-f922-4e8e-9c1c-26f0a2252132" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFD3D529-BCD3-4ECD-9B2A-42924892FFCB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3B4D9D5-B351-46EB-A728-C3362FE437D4}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32608D25-EC36-42FE-A1DC-F778995A6799}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{32608D25-EC36-42FE-A1DC-F778995A6799}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2000/xmlns/"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="851b35d3-0456-4d6a-bc2f-da927e91d158"/>
+    <ds:schemaRef ds:uri="19483571-f922-4e8e-9c1c-26f0a2252132"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E3B4D9D5-B351-46EB-A728-C3362FE437D4}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FFD3D529-BCD3-4ECD-9B2A-42924892FFCB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="19483571-f922-4e8e-9c1c-26f0a2252132"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="851b35d3-0456-4d6a-bc2f-da927e91d158"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>